--- a/supplementary/ESM_2.xlsx
+++ b/supplementary/ESM_2.xlsx
@@ -432,7 +432,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: Edge-level causal graph comparison across 33 TCGA cohorts reveals tissue-specific regulatory structure and prognostic hub genes</t>
+          <t>Article title: A CXCL9–CXCL10–CXCL11 chemokine cascade is the only reproducible cross-cancer causal chain across 33 TCGA cohorts</t>
         </is>
       </c>
     </row>

--- a/supplementary/ESM_2.xlsx
+++ b/supplementary/ESM_2.xlsx
@@ -432,7 +432,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: A CXCL9–CXCL10–CXCL11 chemokine cascade is the only reproducible cross-cancer causal chain across 33 TCGA cohorts</t>
+          <t>Article title: Panel alignment is a precondition for cross-cancer causal comparison: the reproducible structure across 33 TCGA cohorts is a microenvironmental chemokine axis</t>
         </is>
       </c>
     </row>

--- a/supplementary/ESM_2.xlsx
+++ b/supplementary/ESM_2.xlsx
@@ -432,7 +432,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: Panel alignment is a precondition for cross-cancer causal comparison: the reproducible structure across 33 TCGA cohorts is a microenvironmental chemokine axis</t>
+          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis recovered only from aligned gene panels</t>
         </is>
       </c>
     </row>

--- a/supplementary/ESM_2.xlsx
+++ b/supplementary/ESM_2.xlsx
@@ -432,14 +432,14 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis recovered only from aligned gene panels</t>
+          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis of the microenvironment</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Journal: Functional &amp; Integrative Genomics</t>
+          <t>Journal: Network Modeling Analysis in Health Informatics and Bioinformatics</t>
         </is>
       </c>
     </row>
